--- a/paper/Tables/show_up.xlsx
+++ b/paper/Tables/show_up.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAC6258-BA60-4EC0-BB63-3397B38D3E9A}" xr6:coauthVersionLast="33" xr6:coauthVersionMax="33" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
   </bookViews>
   <sheets>
     <sheet name="show_up" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="179017" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
@@ -115,34 +115,34 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +465,7 @@
     <col min="1" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15" thickBot="true" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="11" t="s">
         <v>3</v>
@@ -477,7 +477,7 @@
       </c>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.6" thickTop="true" thickBot="true" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="15" thickTop="true" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -519,23 +519,23 @@
         <f t="shared" ref="F4" si="2">ROUND(L4,3)</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="H4">
-        <v>0.19125683060109289</v>
-      </c>
-      <c r="I4">
-        <v>0.19373219373219372</v>
+      <c r="H4" s="2">
+        <v>0.19314641744548286</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.19682539682539682</v>
       </c>
       <c r="J4">
         <v>0.15921787709497207</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>0.12204724409448819</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>0.16510903426791276</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -559,23 +559,23 @@
         <f t="shared" ref="F5:F6" si="6">ROUND(L5,3)</f>
         <v>0.85299999999999998</v>
       </c>
-      <c r="H5">
-        <v>0.84426229508196726</v>
-      </c>
-      <c r="I5">
-        <v>0.83475783475783472</v>
+      <c r="H5" s="2">
+        <v>0.84735202492211836</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.83174603174603179</v>
       </c>
       <c r="J5">
         <v>0.84636871508379885</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>0.85039370078740162</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>0.85306334371754933</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="15" thickBot="true" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
@@ -599,23 +599,23 @@
         <f t="shared" si="6"/>
         <v>0.44500000000000001</v>
       </c>
-      <c r="H6">
-        <v>0.74590163934426235</v>
-      </c>
-      <c r="I6">
-        <v>0.77207977207977208</v>
+      <c r="H6" s="2">
+        <v>0.73831775700934577</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.76190476190476186</v>
       </c>
       <c r="J6">
         <v>0.7988826815642458</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>0.43438320209973752</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>0.44496365524402909</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="7" ht="15" thickTop="true" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
